--- a/data/potential_queries/queries_type_4.xlsx
+++ b/data/potential_queries/queries_type_4.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Queries" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,22 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,42 +415,34 @@
   </sheetPr>
   <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>query_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>query_type</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>query_texts</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>expected_doc_ids</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>filter_criteria</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -472,10 +454,8 @@
           <t>Q4_001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B2" t="n">
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,7 +464,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>["NK-EL5cFqL5pRrFRBSUjny38g", "NK-FoHPKahRH6oYTxbT7Tycjk", "NK-AJdA3Gt5CuYSxKVuUAfQfy", "NK-B95TF42hNDRBtmaRrW4wwp", "NK-fjaabCsg83J67wd2T3LXoP"]</t>
+          <t>["NK-EL5cFqL5pRrFRBSUjny38g", "NK-FoHPKahRH6oYTxbT7Tycjk", "NK-AJdA3Gt5CuYSxKVuUAfQfy", "NK-B95TF42hNDRBtmaRrW4wwp", "NK-fjaabCsg83J67wd2T3LXoP", "NK-5TRJmJdGoAUdqQSsi7Lz6a"]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -500,10 +480,8 @@
           <t>Q4_002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B3" t="n">
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -528,10 +506,8 @@
           <t>Q4_003</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B4" t="n">
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -556,10 +532,8 @@
           <t>Q4_004</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B5" t="n">
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -568,7 +542,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>["NK-fjaabCsg83J67wd2T3LXoP", "NK-EL5cFqL5pRrFRBSUjny38g", "NK-FoHPKahRH6oYTxbT7Tycjk", "NK-AJdA3Gt5CuYSxKVuUAfQfy"]</t>
+          <t>["NK-fjaabCsg83J67wd2T3LXoP", "NK-EL5cFqL5pRrFRBSUjny38g", "NK-FoHPKahRH6oYTxbT7Tycjk", "NK-AJdA3Gt5CuYSxKVuUAfQfy", "NK-AHmLBXShgacRH3Doimkdv7", "NK-CFYtLmQ52VmAVQZwyTNHKY", "NK-EgaDHFsaqRWDPrZHnNGvnC", "NK-L2aciRRmEVreWptGzTA5MQ", "NK-MGT5v2PXdU8VNueqqkKkLZ", "NK-QrE26F2CD8REmkVWj2btmJ", "NK-RNLrSTsR2ixTEVWMeJprzC", "NK-T99fVT6rNS6tGYTK3mRfGN", "NK-Z9eXoXqGmXo75eJ6CQCXaV", "NK-bCjPZb28YG549GoacB5PvD", "NK-e5V58AvucQkT5E3H6EMd2C", "NK-euCcvPeH3UduiJAFhgdYQh", "NK-h5ym5GPdFihTrS3PzR8ipB", "NK-hL3Xv56XN3YqB5QYVcCa22", "NK-hyKMzKozPsV2LaNZtDqqoC", "NK-n5Bf2hEsizAPpz4cvjkuTT"]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -584,10 +558,8 @@
           <t>Q4_005</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -596,7 +568,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>["NK-EL5cFqL5pRrFRBSUjny38g", "Q112041861", "NK-eXzFarXNX73XPhYRp9xM33"]</t>
+          <t>["NK-EL5cFqL5pRrFRBSUjny38g", "Q112041861", "NK-eXzFarXNX73XPhYRp9xM33", "NK-9AU6V8ADXZysHRebqhpGz8", "NK-B95TF42hNDRBtmaRrW4wwp", "NK-BxdfrmWUHNQUUCj5FE6tQt", "NK-SA8vmm8evWo5zUoVeN6g3H", "NK-WDwNKSpjEwTaniJGoPAWTU", "NK-g5c4xwc3CuQobtZZtNL64i"]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -612,10 +584,8 @@
           <t>Q4_006</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -624,7 +594,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>["Q36597284", "NK-Z9oNBzxf4NzcB6GKXwgPUL", "Q20850503", "NK-SGoKLj97jDeyJGnSyRhJJN", "NK-h2aV4Qyf26ZsX33pRzHRDc", "Q120853746", "Q107586452"]</t>
+          <t>["Q36597284", "NK-Z9oNBzxf4NzcB6GKXwgPUL", "Q20850503", "NK-SGoKLj97jDeyJGnSyRhJJN", "NK-h2aV4Qyf26ZsX33pRzHRDc", "Q120853746", "Q107586452", "Q120851545", "Q120851800", "Q120852137", "Q120852209", "Q120853194", "Q120853202", "Q120853334", "Q120853399", "Q120853453", "Q120853792", "Q120854113", "Q120854828", "Q120854870", "Q120855240", "Q120855520", "Q120855805"]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -640,10 +610,8 @@
           <t>Q4_007</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -652,7 +620,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>["Q120852793", "NK-N7dfJjNtqB9hibmDaoviPf", "NK-TsnsTYDD5QeZ9gDbFB2WbU", "NK-3MPTNLvV5pezgcPmtqapAM", "NK-mFuJH7pUGnr7fegsQYbRWp", "NK-8H4ADaELozj4fx4NYAYZjF", "NK-n8gyfuPWedBXSbpTnLarj8", "NK-YHHfaWGJ4rhJczQmJrZVfC", "NK-Za9Z4Nz5aGAWsd3B8H4VrT"]</t>
+          <t>["Q120852793", "NK-N7dfJjNtqB9hibmDaoviPf", "NK-TsnsTYDD5QeZ9gDbFB2WbU", "NK-3MPTNLvV5pezgcPmtqapAM", "NK-mFuJH7pUGnr7fegsQYbRWp", "NK-8H4ADaELozj4fx4NYAYZjF", "NK-n8gyfuPWedBXSbpTnLarj8", "NK-YHHfaWGJ4rhJczQmJrZVfC", "NK-Za9Z4Nz5aGAWsd3B8H4VrT", "Q120851545", "Q120851800", "Q120852137", "Q120852209", "Q120853194", "Q120853202", "Q120853334", "Q120853399", "Q120853453", "Q120853792", "Q120854113", "Q120854828", "Q120854870", "Q120855240", "Q120855520", "Q120855805"]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -668,10 +636,8 @@
           <t>Q4_008</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B9" t="n">
+        <v>4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -680,7 +646,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>["Q20850503", "Q36597284", "NK-Z9oNBzxf4NzcB6GKXwgPUL", "Q120852793"]</t>
+          <t>["Q20850503", "Q36597284", "NK-Z9oNBzxf4NzcB6GKXwgPUL", "Q120852793", "NK-K8SU4SNzr9PEYs6wc9r4VT", "Q117874377", "Q117874730", "Q117875033", "acf-4f2df6168a6e6dd0795d5d3134c74f6ade51303e"]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -696,10 +662,8 @@
           <t>Q4_009</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B10" t="n">
+        <v>4</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -724,10 +688,8 @@
           <t>Q4_010</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B11" t="n">
+        <v>4</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -752,10 +714,8 @@
           <t>Q4_011</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B12" t="n">
+        <v>4</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -764,7 +724,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>["NK-kNULoiM7XfTYeWLtTZ4UHg", "NK-jLcvcAFxBd2aYNeqUvit3a", "NK-hQEF3vmPJKUQshxZRMEEgo", "NK-9iiiphJsGDHoyN8WZuof3Q"]</t>
+          <t>["NK-kNULoiM7XfTYeWLtTZ4UHg", "NK-jLcvcAFxBd2aYNeqUvit3a", "NK-hQEF3vmPJKUQshxZRMEEgo", "NK-9iiiphJsGDHoyN8WZuof3Q", "NK-WEiG5L6au7ktRSmXSPbBjE"]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -780,10 +740,8 @@
           <t>Q4_012</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B13" t="n">
+        <v>4</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -808,10 +766,8 @@
           <t>Q4_013</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B14" t="n">
+        <v>4</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -836,10 +792,8 @@
           <t>Q4_014</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B15" t="n">
+        <v>4</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -848,7 +802,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>["NK-jF6xZDZzsiGDtJtGcBqoLi", "NK-Nz46UHrXiSCEWLkEQTdoPb", "NK-f8wa3QmkpZDMtjiA6AkMns", "NK-AmRGwyzifJDB2PHBJTGyyM", "NK-f24scmxDu6J7gRYcS6nbKt", "NK-eih3utdAN5JxttKvdA2C7y"]</t>
+          <t>["NK-jF6xZDZzsiGDtJtGcBqoLi", "NK-Nz46UHrXiSCEWLkEQTdoPb", "NK-f8wa3QmkpZDMtjiA6AkMns", "NK-AmRGwyzifJDB2PHBJTGyyM", "NK-f24scmxDu6J7gRYcS6nbKt", "NK-eih3utdAN5JxttKvdA2C7y", "NK-5PJzeksBUtpVFoJHPNXeGj", "NK-dk49S4xLEYXiKGHp3tqGSn", "ca-sema-c75daea1cd04a9a94bed022dfe2fe1e284e4f77f"]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
